--- a/aifes-rubric/AIFES2026_グランドフィナーレ_AI予備審査ルーブリック.xlsx
+++ b/aifes-rubric/AIFES2026_グランドフィナーレ_AI予備審査ルーブリック.xlsx
@@ -795,7 +795,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="436">
   <si>
     <r>
       <rPr>
@@ -1178,7 +1178,24 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">点に正規化した。</t>
+      <t xml:space="preserve">点に正規化したうえで、扱いやすさのため</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点刻みに丸めている。</t>
     </r>
     <r>
       <rPr>
@@ -1649,7 +1666,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">18 </t>
+      <t xml:space="preserve">20 </t>
     </r>
     <r>
       <rPr>
@@ -1683,15 +1700,32 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">17.8%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）　主な出所：</t>
+      <t xml:space="preserve">17.8% → 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点刻みに丸めて </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）　問い：</t>
     </r>
     <r>
       <rPr>
@@ -1774,15 +1808,32 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20.0%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）　主な出所：部門の何割が、当たり前のこととして使っているか。主役は誰か。</t>
+      <t xml:space="preserve">20.0% → 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点刻みに丸めて </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）　問い：部門の何割が、当たり前のこととして使っているか。主役は誰か。</t>
     </r>
   </si>
   <si>
@@ -1814,7 +1865,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">11 </t>
+      <t xml:space="preserve">10 </t>
     </r>
     <r>
       <rPr>
@@ -1848,15 +1899,32 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">11.1%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）　主な出所：担当者が抜けても回るか。他部門が実際に再利用しているか。</t>
+      <t xml:space="preserve">11.1% → 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点刻みに丸めて </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）　問い：担当者が抜けても回るか。他部門が実際に再利用しているか。</t>
     </r>
   </si>
   <si>
@@ -1888,7 +1956,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">22 </t>
+      <t xml:space="preserve">20 </t>
     </r>
     <r>
       <rPr>
@@ -1922,15 +1990,32 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">22.2%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）　主な出所：自部門で閉じているか、面で会社を、さらに顧客を引き上げているか。</t>
+      <t xml:space="preserve">22.2% → 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点刻みに丸めて </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）　問い：自部門で閉じているか、面で会社を、さらに顧客を引き上げているか。</t>
     </r>
   </si>
   <si>
@@ -1962,7 +2047,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">9 </t>
+      <t xml:space="preserve">10 </t>
     </r>
     <r>
       <rPr>
@@ -1996,15 +2081,32 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8.9%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）　主な出所：浮いた時間はどこへ行ったか。二段・三段先とつながっているか。</t>
+      <t xml:space="preserve">8.9% → 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点刻みに丸めて </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）　問い：浮いた時間はどこへ行ったか。二段・三段先とつながっているか。</t>
     </r>
   </si>
   <si>
@@ -2070,15 +2172,32 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20.0%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）　主な出所：本人の言葉か。借り物の言葉か。聞き手が引き込まれるか。</t>
+      <t xml:space="preserve">20.0% → 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点刻みに丸めて </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）　問い：本人の言葉か。借り物の言葉か。聞き手が引き込まれるか。</t>
     </r>
   </si>
   <si>
@@ -3521,7 +3640,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(18</t>
+      <t xml:space="preserve">(20</t>
     </r>
     <r>
       <rPr>
@@ -3635,7 +3754,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(11</t>
+      <t xml:space="preserve">(10</t>
     </r>
     <r>
       <rPr>
@@ -3692,7 +3811,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(22</t>
+      <t xml:space="preserve">(20</t>
     </r>
     <r>
       <rPr>
@@ -3749,7 +3868,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(9</t>
+      <t xml:space="preserve">(10</t>
     </r>
     <r>
       <rPr>
@@ -4114,7 +4233,28 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">点に正規化）</t>
+      <t xml:space="preserve">点に正規化 → </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点刻み）</t>
     </r>
   </si>
   <si>
@@ -6175,34 +6315,120 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配点の大きい観点（</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C4→C2→C6→C1</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点刻みに丸めた結果、</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）から順に見るのが原則だが、</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C1</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は同じ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点で並ぶため、配点の大小では順序が決まらない。同点が出た場合は、書面から実態を読み取りやすい観点を優先する。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -6216,64 +6442,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（当事者性と熱量）は当日のプレゼンで印象が変わりうるため、予備審査のタイブレークでは組織の実態を示す</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を優先している。</t>
+      <t xml:space="preserve">（当事者性と熱量）は当日のプレゼンで印象が変わりうるため最後に置いている。</t>
     </r>
   </si>
   <si>
@@ -6860,7 +7029,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">18 </t>
+      <t xml:space="preserve">20 </t>
     </r>
     <r>
       <rPr>
@@ -7761,7 +7930,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">11 </t>
+      <t xml:space="preserve">10 </t>
     </r>
     <r>
       <rPr>
@@ -8003,7 +8172,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">22 </t>
+      <t xml:space="preserve">20 </t>
     </r>
     <r>
       <rPr>
@@ -8346,7 +8515,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">9 </t>
+      <t xml:space="preserve">10 </t>
     </r>
     <r>
       <rPr>
@@ -9749,7 +9918,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">": 18,</t>
+      <t xml:space="preserve">": 20,</t>
     </r>
   </si>
   <si>
@@ -10041,6 +10210,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">      "id": "C3",</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -10056,6 +10228,51 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">名称</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">": "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仕組み化と会社のプロセス資産化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">",</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">      "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">配点</t>
     </r>
     <r>
@@ -10065,11 +10282,11 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">": 20,</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">      "id": "C3",</t>
+      <t xml:space="preserve">": 10,</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">      "id": "C4",</t>
   </si>
   <si>
     <r>
@@ -10104,7 +10321,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">仕組み化と会社のプロセス資産化</t>
+      <t xml:space="preserve">波及範囲と経営視座</t>
     </r>
     <r>
       <rPr>
@@ -10117,6 +10334,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">      "id": "C5",</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -10132,37 +10352,6 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">配点</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Consolas"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">": 11,</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">      "id": "C4",</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Consolas"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">      "</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">名称</t>
     </r>
     <r>
@@ -10180,7 +10369,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">波及範囲と経営視座</t>
+      <t xml:space="preserve">創出した価値と、その再投資先</t>
     </r>
     <r>
       <rPr>
@@ -10190,110 +10379,6 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">",</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Consolas"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">      "</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配点</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Consolas"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">": 22,</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">      "id": "C5",</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Consolas"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">      "</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">名称</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Consolas"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">": "</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">創出した価値と、その再投資先</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Consolas"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">",</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Consolas"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">      "</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配点</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Consolas"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">": 9,</t>
     </r>
   </si>
   <si>
@@ -12006,7 +12091,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.#"/>
     <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
   <fonts count="31">
@@ -12596,7 +12681,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -13114,7 +13199,7 @@
         <v>43</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" s="16" t="n">
         <v>5</v>
@@ -13270,7 +13355,7 @@
         <v>61</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18" s="16" t="n">
         <v>5</v>
@@ -13348,7 +13433,7 @@
         <v>70</v>
       </c>
       <c r="C25" s="15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D25" s="16" t="n">
         <v>5</v>
@@ -13426,7 +13511,7 @@
         <v>79</v>
       </c>
       <c r="C32" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D32" s="16" t="n">
         <v>5</v>
@@ -14001,19 +14086,19 @@
         <v>138</v>
       </c>
       <c r="D18" s="32" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>20</v>
       </c>
       <c r="F18" s="32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18" s="32" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H18" s="32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I18" s="32" t="n">
         <v>20</v>
@@ -14210,19 +14295,19 @@
         <v>166</v>
       </c>
       <c r="D5" s="35" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5" s="35" t="n">
         <v>20</v>
       </c>
       <c r="F5" s="35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" s="35" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H5" s="35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" s="35" t="n">
         <v>20</v>
@@ -14265,7 +14350,7 @@
       </c>
       <c r="J6" s="40" t="n">
         <f aca="false">IF(D6="","",ROUND(D6/5*$D$5,1))</f>
-        <v>14.4</v>
+        <v>16</v>
       </c>
       <c r="K6" s="40" t="n">
         <f aca="false">IF(E6="","",ROUND(E6/5*$E$5,1))</f>
@@ -14273,15 +14358,15 @@
       </c>
       <c r="L6" s="40" t="n">
         <f aca="false">IF(F6="","",ROUND(F6/5*$F$5,1))</f>
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="M6" s="40" t="n">
         <f aca="false">IF(G6="","",ROUND(G6/5*$G$5,1))</f>
-        <v>17.6</v>
+        <v>16</v>
       </c>
       <c r="N6" s="40" t="n">
         <f aca="false">IF(H6="","",ROUND(H6/5*$H$5,1))</f>
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="O6" s="40" t="n">
         <f aca="false">IF(I6="","",ROUND(I6/5*$I$5,1))</f>
@@ -14289,7 +14374,7 @@
       </c>
       <c r="P6" s="41" t="n">
         <f aca="false">IF(COUNT(D6:I6)&lt;6,"",ROUND(SUM(J6:O6),1))</f>
-        <v>85.8</v>
+        <v>86</v>
       </c>
       <c r="Q6" s="42" t="str">
         <f aca="false">IF(P6="","",IF(P6&gt;=80,"S",IF(P6&gt;=65,"A",IF(P6&gt;=50,"B","C"))))</f>
@@ -17351,7 +17436,7 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B191" s="63" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17381,12 +17466,12 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B197" s="63" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B198" s="63" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17396,7 +17481,7 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B200" s="63" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17426,12 +17511,12 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B206" s="63" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B207" s="63" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17441,7 +17526,7 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B209" s="63" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17471,12 +17556,12 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B215" s="63" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B216" s="63" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17486,7 +17571,7 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B218" s="63" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17516,12 +17601,12 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B224" s="63" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B225" s="63" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17531,7 +17616,7 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B227" s="63" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17551,17 +17636,17 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B231" s="63" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B232" s="63" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B233" s="63" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17571,17 +17656,17 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B235" s="63" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B236" s="63" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B237" s="63" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17596,17 +17681,17 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B240" s="63" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B241" s="63" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B242" s="63" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17621,17 +17706,17 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B245" s="63" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B246" s="63" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B247" s="63" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17646,72 +17731,72 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B250" s="63" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B251" s="63" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B252" s="63" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B253" s="63" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B254" s="63" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B255" s="63" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B256" s="63" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B257" s="63" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B258" s="63" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B259" s="63" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B260" s="63" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B261" s="63" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B262" s="63" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B263" s="63" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17724,7 +17809,7 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B266" s="62" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17734,27 +17819,27 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B268" s="62" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B269" s="62" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B270" s="62" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B271" s="62" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B272" s="62" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17767,7 +17852,7 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B275" s="62" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17806,7 +17891,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="23" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -17816,7 +17901,7 @@
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -17835,13 +17920,13 @@
         <v>100</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17855,13 +17940,13 @@
         <v>108</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E4" s="64" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="F4" s="65" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17875,13 +17960,13 @@
         <v>111</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E5" s="64" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="F5" s="65" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17895,13 +17980,13 @@
         <v>114</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E6" s="64" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F6" s="65" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17915,13 +18000,13 @@
         <v>114</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="E7" s="66" t="s">
         <v>413</v>
       </c>
-      <c r="E7" s="66" t="s">
-        <v>416</v>
-      </c>
       <c r="F7" s="67" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17935,13 +18020,13 @@
         <v>114</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E8" s="66" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="F8" s="65" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17955,13 +18040,13 @@
         <v>114</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E9" s="66" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="F9" s="65" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17975,13 +18060,13 @@
         <v>119</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E10" s="64" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F10" s="67" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17995,13 +18080,13 @@
         <v>121</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E11" s="64" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="F11" s="65" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18015,13 +18100,13 @@
         <v>123</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E12" s="64" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F12" s="65" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18035,13 +18120,13 @@
         <v>125</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E13" s="66" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F13" s="65" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18055,13 +18140,13 @@
         <v>127</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E14" s="66" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F14" s="67" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18075,13 +18160,13 @@
         <v>129</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E15" s="66" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F15" s="65" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>

--- a/aifes-rubric/AIFES2026_グランドフィナーレ_AI予備審査ルーブリック.xlsx
+++ b/aifes-rubric/AIFES2026_グランドフィナーレ_AI予備審査ルーブリック.xlsx
@@ -12,9 +12,10 @@
     <sheet name="01_ルーブリック" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="02_審査員対応表" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="03_採点シート" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="04_判定ルールとフラグ" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="05_AI審査プロンプト" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="06_元データ_審査員コメント" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="04_役員予備審査投票" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="05_判定ルールとフラグ" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="06_AI審査プロンプト" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="07_元データ_審査員コメント" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -773,7 +774,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="448">
   <si>
     <r>
       <rPr>
@@ -986,7 +987,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">06_</t>
+      <t xml:space="preserve">07_</t>
     </r>
     <r>
       <rPr>
@@ -1340,17 +1341,328 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF1F3864"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">応募が</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF1F3864"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件のとき</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">04_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">役員予備審査投票 シートで、役員</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の評価を参考に上位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部へ順位をつける。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点の配点と「各役員の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位は無条件で決勝進出」のルールで、決勝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部を自動判定する。応募が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件以下ならこのシートは使わず、全件がそのまま決勝進出する。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -1365,7 +1677,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">05_AI</t>
+      <t xml:space="preserve">06_AI</t>
     </r>
     <r>
       <rPr>
@@ -4156,7 +4468,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">06_</t>
+      <t xml:space="preserve">07_</t>
     </r>
     <r>
       <rPr>
@@ -5311,7 +5623,321 @@
     <t xml:space="preserve">上限超過あり</t>
   </si>
   <si>
-    <t xml:space="preserve">判定バンド・前提フラグ・タイブレーク</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="16"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">役員予備審査 投票集計（応募</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="16"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="16"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="16"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="16"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件のときだけ使用）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">応募</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件以下なら全件がそのまま決勝進出。このシートは使わない。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件のときだけ、役員</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の評価（③列</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">03_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採点シートより自動参照）を参考に上位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部へ順位をつけ、下の配点で決勝進出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部を自動判定する。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">① 応募一覧（部門名を入力。②のドロップダウンと③の集計の元になる）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">※ 03_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採点シートの部門名と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">文字違わず同じ表記で入力すること（一致しないと</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">参考値が引けない）。</t>
+    </r>
   </si>
   <si>
     <r>
@@ -5319,710 +5945,1338 @@
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF1F3864"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1. </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">② 役員</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF1F3864"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">総合判定バンド</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">総合点</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予備審査での扱い</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">80 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">点以上</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">グランドフィナーレ最有力。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">観点のいずれにも穴がない。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">A</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">65 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">点以上</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">通過候補。人手審査へ回す。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">50 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">点以上</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">要議論。強い観点があれば人手審査で拾い上げる。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">50 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">点未満</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">予備審査で見送り。</t>
-  </si>
-  <si>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF1F3864"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2. </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名の投票（①の</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF1F3864"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">前提フラグ（加点ではなく、該当観点にレベル上限をかける）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ID / </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">名称</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">どう見分けるか</t>
-  </si>
-  <si>
-    <t xml:space="preserve">かかる上限</t>
-  </si>
-  <si>
-    <t xml:space="preserve">根拠となった審査員の言葉</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">F1  </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">生産性向上の数値のみ</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">時短・削減の数値は並ぶが、文化・浸透・参加率に関する記述がない。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">組織への広がり・定着 はレベル </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以下</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">櫻田 浩：生産性向上につながる活用は重要だが、それは企業として取り組むべき前提。／ 中山 高史：何を</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">AI</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">で実現したかよりも、部門にどのような文化を醸成できたか。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">F2  </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">特定個人</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">名の成果</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">登場する実行者が実質</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">名で、部門への広がりも仕組みも語られていない。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">組織への広がり・定着 はレベル </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以下 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ C3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">人・チームの変化 はレベル </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以下 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ C5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">再現性・資産化 はレベル </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以下</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">伊藤 裕一：特定の誰かに頼るのではなく、チーム全員を巻き込んで。／ 松尾 邦孝：個人の熱意に依存しているのか、組織として自律的に回っているのか。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">F3  </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ツール導入・</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PoC</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">止まり</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">導入した／試したという報告で終わり、業務そのものの変化が示されていない。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">業務変革 はレベル </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以下</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">前田 憲仁：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を付加的に活用するのではなく、業務プロセス自体を見直せているか。／ 中村 智之：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を使ったこと自体ではなく、その結果として業務や事業がどれだけ変わったか。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">F4  </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本人の言葉でない</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">部門長本人の一人称の語りがなく、事務局資料や代理者の説明の引き写しになっている。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">人・チームの変化 はレベル </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以下</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">上坂 貴志：取り組みを自分の言葉で語れる人が前に立っているか。／ 牧田 幸弘：自分自身の言葉で価値を語れるかどうか。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">採点シートの </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">W</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列「上限チェック」が、フラグと入力レベルの矛盾を自動検出する。「上限超過」と出たら、該当観点のレベルを上限まで下げる。</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF1F3864"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3. </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">評価を参考に、上位</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="12"/>
         <color rgb="FF1F3864"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部へ順位をつける）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">審査員名</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">※ 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位は同じ役員の中で重複させないこと（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列が「★重複あり」なら入力し直す）。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">③ 得点集計・決勝進出判定（自動計算）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配点：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位以下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点（役員</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名分の合計・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点満点）。各役員の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位に選ばれた部門は、合計点に関わらず無条件で決勝進出（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位保護ルール）。残りの枠は合計点の高い順で埋める。同点の場合は ①</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位票の数 → ②</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位票の数 → ③</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名の合議、で決める。予選の点数・順位は非公開。本番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名の最終順位には加算しない（登壇順の決定と、本番同点時のタイブレークにのみ使用）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">J</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列（内部計算用）は決勝進出の判定に使う優先度スコアで、触らない。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位保護に該当する部門は常に非該当より上位になるよう十分大きい値を足してある。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">判定バンド・前提フラグ・タイブレーク</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">総合判定バンド</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">総合点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">予備審査での扱い</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点以上</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">グランドフィナーレ最有力。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">観点のいずれにも穴がない。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">65 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点以上</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">通過候補。人手審査へ回す。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点以上</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">要議論。強い観点があれば人手審査で拾い上げる。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点未満</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">予備審査で見送り。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前提フラグ（加点ではなく、該当観点にレベル上限をかける）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ID / </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名称</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">どう見分けるか</t>
+  </si>
+  <si>
+    <t xml:space="preserve">かかる上限</t>
+  </si>
+  <si>
+    <t xml:space="preserve">根拠となった審査員の言葉</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F1  </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">生産性向上の数値のみ</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">時短・削減の数値は並ぶが、文化・浸透・参加率に関する記述がない。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">組織への広がり・定着 はレベル </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以下</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">櫻田 浩：生産性向上につながる活用は重要だが、それは企業として取り組むべき前提。／ 中山 高史：何を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で実現したかよりも、部門にどのような文化を醸成できたか。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F2  </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">特定個人</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名の成果</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">登場する実行者が実質</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名で、部門への広がりも仕組みも語られていない。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">組織への広がり・定着 はレベル </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以下 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ C3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人・チームの変化 はレベル </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以下 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ C5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">再現性・資産化 はレベル </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以下</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">伊藤 裕一：特定の誰かに頼るのではなく、チーム全員を巻き込んで。／ 松尾 邦孝：個人の熱意に依存しているのか、組織として自律的に回っているのか。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F3  </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ツール導入・</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PoC</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">止まり</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">導入した／試したという報告で終わり、業務そのものの変化が示されていない。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">業務変革 はレベル </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以下</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前田 憲仁：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を付加的に活用するのではなく、業務プロセス自体を見直せているか。／ 中村 智之：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を使ったこと自体ではなく、その結果として業務や事業がどれだけ変わったか。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F4  </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本人の言葉でない</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">部門長本人の一人称の語りがなく、事務局資料や代理者の説明の引き写しになっている。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人・チームの変化 はレベル </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以下</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">上坂 貴志：取り組みを自分の言葉で語れる人が前に立っているか。／ 牧田 幸弘：自分自身の言葉で価値を語れるかどうか。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採点シートの </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">W</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列「上限チェック」が、フラグと入力レベルの矛盾を自動検出する。「上限超過」と出たら、該当観点のレベルを上限まで下げる。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6063,27 +7317,19 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">総合得点（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">観点の素点合計・</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">他部門・全社への波及と未来 のレベルが高いほうを上位とする（配点</t>
     </r>
     <r>
       <rPr>
@@ -6100,7 +7346,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">点満点） のレベルが高いほうを上位とする</t>
+      <t xml:space="preserve">点で最重）</t>
     </r>
   </si>
   <si>
@@ -6137,27 +7383,36 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">傾斜配分後の得点（観点の配点で加重・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">点満点） のレベルが高いほうを上位とする</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">組織への広がり・定着 のレベルが高いほうを上位とする（次点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点）</t>
     </r>
   </si>
   <si>
@@ -6194,27 +7449,36 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">最高評価「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">」をつけた審査員の数 のレベルが高いほうを上位とする</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">業務変革 のレベルが高いほうを上位とする（同じく</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点）</t>
     </r>
   </si>
   <si>
@@ -6248,7 +7512,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">社長が順位を決定 のレベルが高いほうを上位とする</t>
+    <t xml:space="preserve">それでも並ぶ場合は、事務局・役員の合議で決定する</t>
   </si>
   <si>
     <r>
@@ -6297,45 +7561,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">C2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C6 </t>
+      <t xml:space="preserve">C2 </t>
     </r>
     <r>
       <rPr>
@@ -6363,7 +7589,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">点で並ぶため、配点の大小では順序が決まらない。同点が出た場合は、書面から実態を読み取りやすい観点を優先する。</t>
+      <t xml:space="preserve">点で並ぶ。</t>
     </r>
     <r>
       <rPr>
@@ -6382,7 +7608,45 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（当事者性と熱量）は当日のプレゼンで印象が変わりうるため最後に置いている。</t>
+      <t xml:space="preserve">（他部門・全社への波及と未来）は単独で最も重い</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点なので、まずここのレベル差で決めるのが最も情報量が大きい。それでも並ぶ場合は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C2→C1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の順で見て、最後は事務局・役員の合議とする。</t>
     </r>
   </si>
   <si>
@@ -9459,24 +10723,24 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">同点時のタイブレークは次の順で比較する： 総合得点（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Consolas"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">観点の素点合計・</t>
+      <t xml:space="preserve">同点時のタイブレークは次の順で比較する： </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">他部門・全社への波及と未来 のレベルが高いほうを上位とする（配点</t>
     </r>
     <r>
       <rPr>
@@ -9493,41 +10757,75 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">点満点） → 傾斜配分後の得点（観点の配点で加重・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Consolas"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">点満点） → 最高評価「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Consolas"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">」をつけた審査員の数 → 社長が順位を決定</t>
+      <t xml:space="preserve">点で最重） → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">組織への広がり・定着 のレベルが高いほうを上位とする（次点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点） → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">業務変革 のレベルが高いほうを上位とする（同じく</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点） → それでも並ぶ場合は、事務局・役員の合議で決定する</t>
     </r>
   </si>
   <si>
@@ -12020,7 +13318,7 @@
     <numFmt numFmtId="165" formatCode="0.#"/>
     <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -12211,6 +13509,28 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="14"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
@@ -12366,7 +13686,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="82">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -12591,16 +13911,76 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="28" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -12611,15 +13991,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -12891,7 +14267,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -12949,7 +14325,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -12957,10 +14333,10 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -12972,25 +14348,25 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
+    <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="C11" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7"/>
-      <c r="B13" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="8" t="s">
+      <c r="B13" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="9" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7"/>
+      <c r="B14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="8" t="s">
         <v>21</v>
       </c>
     </row>
@@ -13034,12 +14410,20 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="10" t="s">
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="4" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -13075,7 +14459,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13087,7 +14471,7 @@
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -13099,30 +14483,30 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C4" s="15" t="n">
         <v>20</v>
@@ -13131,10 +14515,10 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13145,7 +14529,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F5" s="17"/>
     </row>
@@ -13157,7 +14541,7 @@
         <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F6" s="17"/>
     </row>
@@ -13169,7 +14553,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F7" s="17"/>
     </row>
@@ -13181,13 +14565,13 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
@@ -13197,10 +14581,10 @@
     </row>
     <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C11" s="15" t="n">
         <v>20</v>
@@ -13209,10 +14593,10 @@
         <v>5</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13223,7 +14607,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F12" s="17"/>
     </row>
@@ -13235,7 +14619,7 @@
         <v>3</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F13" s="17"/>
     </row>
@@ -13247,7 +14631,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F14" s="17"/>
     </row>
@@ -13259,13 +14643,13 @@
         <v>1</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F15" s="17"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="22" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B16" s="22"/>
       <c r="C16" s="22"/>
@@ -13275,10 +14659,10 @@
     </row>
     <row r="18" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C18" s="15" t="n">
         <v>10</v>
@@ -13287,10 +14671,10 @@
         <v>5</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13301,7 +14685,7 @@
         <v>4</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F19" s="17"/>
     </row>
@@ -13313,7 +14697,7 @@
         <v>3</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F20" s="17"/>
     </row>
@@ -13325,7 +14709,7 @@
         <v>2</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F21" s="17"/>
     </row>
@@ -13337,13 +14721,13 @@
         <v>1</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F22" s="17"/>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -13353,10 +14737,10 @@
     </row>
     <row r="25" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C25" s="15" t="n">
         <v>10</v>
@@ -13365,10 +14749,10 @@
         <v>5</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13379,7 +14763,7 @@
         <v>4</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F26" s="17"/>
     </row>
@@ -13391,7 +14775,7 @@
         <v>3</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F27" s="17"/>
     </row>
@@ -13403,7 +14787,7 @@
         <v>2</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F28" s="17"/>
     </row>
@@ -13415,13 +14799,13 @@
         <v>1</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F29" s="17"/>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="22" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
@@ -13431,10 +14815,10 @@
     </row>
     <row r="32" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C32" s="15" t="n">
         <v>10</v>
@@ -13443,10 +14827,10 @@
         <v>5</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13457,7 +14841,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F33" s="17"/>
     </row>
@@ -13469,7 +14853,7 @@
         <v>3</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F34" s="17"/>
     </row>
@@ -13481,7 +14865,7 @@
         <v>2</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F35" s="17"/>
     </row>
@@ -13493,13 +14877,13 @@
         <v>1</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F36" s="17"/>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B37" s="22"/>
       <c r="C37" s="22"/>
@@ -13509,10 +14893,10 @@
     </row>
     <row r="39" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C39" s="15" t="n">
         <v>30</v>
@@ -13521,10 +14905,10 @@
         <v>5</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13535,7 +14919,7 @@
         <v>4</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F40" s="17"/>
     </row>
@@ -13547,7 +14931,7 @@
         <v>3</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F41" s="17"/>
     </row>
@@ -13559,7 +14943,7 @@
         <v>2</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F42" s="17"/>
     </row>
@@ -13571,13 +14955,13 @@
         <v>1</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F43" s="17"/>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
@@ -13648,7 +15032,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -13662,7 +15046,7 @@
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -13676,31 +15060,31 @@
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13708,15 +15092,15 @@
         <v>1</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D4" s="25"/>
       <c r="E4" s="25"/>
       <c r="F4" s="26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G4" s="25"/>
       <c r="H4" s="25"/>
@@ -13727,17 +15111,17 @@
         <v>2</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D5" s="25"/>
       <c r="E5" s="26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G5" s="25"/>
       <c r="H5" s="25"/>
@@ -13748,24 +15132,24 @@
         <v>3</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
       <c r="G6" s="27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13773,18 +15157,18 @@
         <v>4</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" s="27" t="s">
         <v>114</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>112</v>
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
       <c r="G7" s="26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
@@ -13794,18 +15178,18 @@
         <v>5</v>
       </c>
       <c r="B8" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F8" s="25"/>
       <c r="G8" s="27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
@@ -13815,17 +15199,17 @@
         <v>6</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
@@ -13836,10 +15220,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D10" s="25"/>
       <c r="E10" s="25"/>
@@ -13847,7 +15231,7 @@
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
       <c r="I10" s="26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13855,20 +15239,20 @@
         <v>8</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E11" s="25"/>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
       <c r="I11" s="26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13876,19 +15260,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
       <c r="G12" s="25"/>
       <c r="H12" s="26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I12" s="25"/>
     </row>
@@ -13897,21 +15281,21 @@
         <v>10</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F13" s="25"/>
       <c r="G13" s="25"/>
       <c r="H13" s="26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I13" s="25"/>
     </row>
@@ -13920,20 +15304,20 @@
         <v>11</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D14" s="25"/>
       <c r="E14" s="25"/>
       <c r="F14" s="27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G14" s="25"/>
       <c r="H14" s="25"/>
       <c r="I14" s="26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13941,10 +15325,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D15" s="25"/>
       <c r="E15" s="25"/>
@@ -13952,35 +15336,35 @@
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
       <c r="I15" s="26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C16" s="28" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="29" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D17" s="30" t="n">
         <v>4</v>
@@ -14003,7 +15387,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D18" s="32" t="n">
         <v>20</v>
@@ -14026,7 +15410,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B20" s="33"/>
       <c r="C20" s="33"/>
@@ -14077,7 +15461,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="23" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -14106,7 +15490,7 @@
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -14135,84 +15519,84 @@
     </row>
     <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="S4" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="T4" s="7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="U4" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="V4" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="W4" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="X4" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Y4" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="34" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D5" s="35" t="n">
         <v>20</v>
@@ -14237,18 +15621,18 @@
         <v>100</v>
       </c>
       <c r="X5" s="36" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D6" s="39" t="n">
         <v>4</v>
@@ -14301,7 +15685,7 @@
         <v>S</v>
       </c>
       <c r="R6" s="30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="S6" s="39"/>
       <c r="T6" s="39"/>
@@ -14312,10 +15696,10 @@
         <v>OK</v>
       </c>
       <c r="X6" s="38" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Y6" s="44" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16090,7 +17474,7 @@
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="51" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B38" s="51"/>
       <c r="C38" s="51"/>
@@ -16103,12 +17487,12 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="52" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="53" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C41" s="54" t="n">
         <f aca="false">COUNT($P$7:$P$36)</f>
@@ -16117,7 +17501,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="53" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C42" s="54" t="str">
         <f aca="false">IFERROR(ROUND(AVERAGE($P$7:$P$36),1),"")</f>
@@ -16126,7 +17510,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="53" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C43" s="54" t="n">
         <f aca="false">IFERROR(MAX($P$7:$P$36),"")</f>
@@ -16135,7 +17519,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="55" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C44" s="54" t="n">
         <f aca="false">COUNTIF($Q$7:$Q$36,"S")</f>
@@ -16144,7 +17528,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="55" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C45" s="54" t="n">
         <f aca="false">COUNTIF($Q$7:$Q$36,"A")</f>
@@ -16153,7 +17537,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="55" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C46" s="54" t="n">
         <f aca="false">COUNTIF($Q$7:$Q$36,"B")</f>
@@ -16162,7 +17546,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="55" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C47" s="54" t="n">
         <f aca="false">COUNTIF($Q$7:$Q$36,"C")</f>
@@ -16171,7 +17555,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="53" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C48" s="54" t="n">
         <f aca="false">COUNTIF($W$7:$W$36,"上限超過*")</f>
@@ -16213,6 +17597,538 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+    </row>
+    <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+    </row>
+    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="56" t="str">
+        <f aca="false">IF(COUNTA($B$6:$B$11)=0,"部門名をまず①に入力してください。",IF(COUNTA($B$6:$B$11)&lt;=4,"★ 応募"&amp;COUNTA($B$6:$B$11)&amp;"件（4件以下）：このシートは不要です。全件がそのまま決勝進出。②③は空欄のままで構いません。","応募"&amp;COUNTA($B$6:$B$11)&amp;"件：②で役員4名が投票すると、③で決勝4部を自動判定します。"))</f>
+        <v>★ 応募1件（4件以下）：このシートは不要です。全件がそのまま決勝進出。②③は空欄のままで構いません。</v>
+      </c>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="52" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="58" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="57" t="str">
+        <f aca="false">IFERROR(INDEX(03_採点シート!$P$7:$P$36,MATCH($B6,03_採点シート!$B$7:$B$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D6" s="57" t="str">
+        <f aca="false">IFERROR(INDEX(03_採点シート!$Q$7:$Q$36,MATCH($B6,03_採点シート!$B$7:$B$36,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="59"/>
+      <c r="C7" s="45" t="str">
+        <f aca="false">IFERROR(INDEX(03_採点シート!$P$7:$P$36,MATCH($B7,03_採点シート!$B$7:$B$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="45" t="str">
+        <f aca="false">IFERROR(INDEX(03_採点シート!$Q$7:$Q$36,MATCH($B7,03_採点シート!$B$7:$B$36,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="59"/>
+      <c r="C8" s="45" t="str">
+        <f aca="false">IFERROR(INDEX(03_採点シート!$P$7:$P$36,MATCH($B8,03_採点シート!$B$7:$B$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D8" s="45" t="str">
+        <f aca="false">IFERROR(INDEX(03_採点シート!$Q$7:$Q$36,MATCH($B8,03_採点シート!$B$7:$B$36,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="59"/>
+      <c r="C9" s="45" t="str">
+        <f aca="false">IFERROR(INDEX(03_採点シート!$P$7:$P$36,MATCH($B9,03_採点シート!$B$7:$B$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="45" t="str">
+        <f aca="false">IFERROR(INDEX(03_採点シート!$Q$7:$Q$36,MATCH($B9,03_採点シート!$B$7:$B$36,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="59"/>
+      <c r="C10" s="45" t="str">
+        <f aca="false">IFERROR(INDEX(03_採点シート!$P$7:$P$36,MATCH($B10,03_採点シート!$B$7:$B$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="45" t="str">
+        <f aca="false">IFERROR(INDEX(03_採点シート!$Q$7:$Q$36,MATCH($B10,03_採点シート!$B$7:$B$36,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="59"/>
+      <c r="C11" s="45" t="str">
+        <f aca="false">IFERROR(INDEX(03_採点シート!$P$7:$P$36,MATCH($B11,03_採点シート!$B$7:$B$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="45" t="str">
+        <f aca="false">IFERROR(INDEX(03_採点シート!$Q$7:$Q$36,MATCH($B11,03_採点シート!$B$7:$B$36,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="60" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="52" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="58" t="s">
+        <v>191</v>
+      </c>
+      <c r="C15" s="61" t="s">
+        <v>192</v>
+      </c>
+      <c r="D15" s="61" t="s">
+        <v>193</v>
+      </c>
+      <c r="E15" s="61" t="s">
+        <v>194</v>
+      </c>
+      <c r="F15" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="G15" s="62" t="str">
+        <f aca="false">IF(COUNTBLANK($C15:$F15)&gt;0,"",IF(OR(COUNTIF($C15:$F15,$C15)&gt;1,COUNTIF($C15:$F15,$D15)&gt;1,COUNTIF($C15:$F15,$E15)&gt;1,COUNTIF($C15:$F15,$F15)&gt;1),"★重複あり","OK"))</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="59"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="63" t="str">
+        <f aca="false">IF(COUNTBLANK($C16:$F16)&gt;0,"",IF(OR(COUNTIF($C16:$F16,$C16)&gt;1,COUNTIF($C16:$F16,$D16)&gt;1,COUNTIF($C16:$F16,$E16)&gt;1,COUNTIF($C16:$F16,$F16)&gt;1),"★重複あり","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="59"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="63" t="str">
+        <f aca="false">IF(COUNTBLANK($C17:$F17)&gt;0,"",IF(OR(COUNTIF($C17:$F17,$C17)&gt;1,COUNTIF($C17:$F17,$D17)&gt;1,COUNTIF($C17:$F17,$E17)&gt;1,COUNTIF($C17:$F17,$F17)&gt;1),"★重複あり","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="59"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="63" t="str">
+        <f aca="false">IF(COUNTBLANK($C18:$F18)&gt;0,"",IF(OR(COUNTIF($C18:$F18,$C18)&gt;1,COUNTIF($C18:$F18,$D18)&gt;1,COUNTIF($C18:$F18,$E18)&gt;1,COUNTIF($C18:$F18,$F18)&gt;1),"★重複あり","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="60" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="52" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="64" t="str">
+        <f aca="false">IF($B$6="","",$B$6)</f>
+        <v>部門名</v>
+      </c>
+      <c r="C22" s="57" t="n">
+        <f aca="false">IF($B22="","",COUNTIF($C$15:$C$18,$B22))</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="57" t="n">
+        <f aca="false">IF($B22="","",COUNTIF($D$15:$D$18,$B22))</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="57" t="n">
+        <f aca="false">IF($B22="","",COUNTIF($E$15:$E$18,$B22))</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="57" t="n">
+        <f aca="false">IF($B22="","",COUNTIF($F$15:$F$18,$B22))</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="57" t="n">
+        <f aca="false">IF($B22="","",C22*10+D22*8+E22*7+F22*6)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="65" t="str">
+        <f aca="false">IF(OR($B22="",COUNTA($B$6:$B$11)&lt;=4),"",IF(C22&gt;=1,"◎内定",""))</f>
+        <v/>
+      </c>
+      <c r="I22" s="66" t="str">
+        <f aca="false">IF(OR($B22="",COUNTA($B$6:$B$11)&lt;=4),"",IF(RANK(J22,$J$22:$J$27,0)&lt;=4,"◎決勝進出",""))</f>
+        <v/>
+      </c>
+      <c r="J22" s="67" t="n">
+        <f aca="false">IF($B22="","",IF(H22&lt;&gt;"",100000,0)+G22*100+C22*10+D22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="9" t="str">
+        <f aca="false">IF($B$7="","",$B$7)</f>
+        <v/>
+      </c>
+      <c r="C23" s="45" t="str">
+        <f aca="false">IF($B23="","",COUNTIF($C$15:$C$18,$B23))</f>
+        <v/>
+      </c>
+      <c r="D23" s="45" t="str">
+        <f aca="false">IF($B23="","",COUNTIF($D$15:$D$18,$B23))</f>
+        <v/>
+      </c>
+      <c r="E23" s="45" t="str">
+        <f aca="false">IF($B23="","",COUNTIF($E$15:$E$18,$B23))</f>
+        <v/>
+      </c>
+      <c r="F23" s="45" t="str">
+        <f aca="false">IF($B23="","",COUNTIF($F$15:$F$18,$B23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="45" t="str">
+        <f aca="false">IF($B23="","",C23*10+D23*8+E23*7+F23*6)</f>
+        <v/>
+      </c>
+      <c r="H23" s="65" t="str">
+        <f aca="false">IF(OR($B23="",COUNTA($B$6:$B$11)&lt;=4),"",IF(C23&gt;=1,"◎内定",""))</f>
+        <v/>
+      </c>
+      <c r="I23" s="66" t="str">
+        <f aca="false">IF(OR($B23="",COUNTA($B$6:$B$11)&lt;=4),"",IF(RANK(J23,$J$22:$J$27,0)&lt;=4,"◎決勝進出",""))</f>
+        <v/>
+      </c>
+      <c r="J23" s="68" t="str">
+        <f aca="false">IF($B23="","",IF(H23&lt;&gt;"",100000,0)+G23*100+C23*10+D23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="9" t="str">
+        <f aca="false">IF($B$8="","",$B$8)</f>
+        <v/>
+      </c>
+      <c r="C24" s="45" t="str">
+        <f aca="false">IF($B24="","",COUNTIF($C$15:$C$18,$B24))</f>
+        <v/>
+      </c>
+      <c r="D24" s="45" t="str">
+        <f aca="false">IF($B24="","",COUNTIF($D$15:$D$18,$B24))</f>
+        <v/>
+      </c>
+      <c r="E24" s="45" t="str">
+        <f aca="false">IF($B24="","",COUNTIF($E$15:$E$18,$B24))</f>
+        <v/>
+      </c>
+      <c r="F24" s="45" t="str">
+        <f aca="false">IF($B24="","",COUNTIF($F$15:$F$18,$B24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="45" t="str">
+        <f aca="false">IF($B24="","",C24*10+D24*8+E24*7+F24*6)</f>
+        <v/>
+      </c>
+      <c r="H24" s="65" t="str">
+        <f aca="false">IF(OR($B24="",COUNTA($B$6:$B$11)&lt;=4),"",IF(C24&gt;=1,"◎内定",""))</f>
+        <v/>
+      </c>
+      <c r="I24" s="66" t="str">
+        <f aca="false">IF(OR($B24="",COUNTA($B$6:$B$11)&lt;=4),"",IF(RANK(J24,$J$22:$J$27,0)&lt;=4,"◎決勝進出",""))</f>
+        <v/>
+      </c>
+      <c r="J24" s="68" t="str">
+        <f aca="false">IF($B24="","",IF(H24&lt;&gt;"",100000,0)+G24*100+C24*10+D24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="9" t="str">
+        <f aca="false">IF($B$9="","",$B$9)</f>
+        <v/>
+      </c>
+      <c r="C25" s="45" t="str">
+        <f aca="false">IF($B25="","",COUNTIF($C$15:$C$18,$B25))</f>
+        <v/>
+      </c>
+      <c r="D25" s="45" t="str">
+        <f aca="false">IF($B25="","",COUNTIF($D$15:$D$18,$B25))</f>
+        <v/>
+      </c>
+      <c r="E25" s="45" t="str">
+        <f aca="false">IF($B25="","",COUNTIF($E$15:$E$18,$B25))</f>
+        <v/>
+      </c>
+      <c r="F25" s="45" t="str">
+        <f aca="false">IF($B25="","",COUNTIF($F$15:$F$18,$B25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="45" t="str">
+        <f aca="false">IF($B25="","",C25*10+D25*8+E25*7+F25*6)</f>
+        <v/>
+      </c>
+      <c r="H25" s="65" t="str">
+        <f aca="false">IF(OR($B25="",COUNTA($B$6:$B$11)&lt;=4),"",IF(C25&gt;=1,"◎内定",""))</f>
+        <v/>
+      </c>
+      <c r="I25" s="66" t="str">
+        <f aca="false">IF(OR($B25="",COUNTA($B$6:$B$11)&lt;=4),"",IF(RANK(J25,$J$22:$J$27,0)&lt;=4,"◎決勝進出",""))</f>
+        <v/>
+      </c>
+      <c r="J25" s="68" t="str">
+        <f aca="false">IF($B25="","",IF(H25&lt;&gt;"",100000,0)+G25*100+C25*10+D25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="9" t="str">
+        <f aca="false">IF($B$10="","",$B$10)</f>
+        <v/>
+      </c>
+      <c r="C26" s="45" t="str">
+        <f aca="false">IF($B26="","",COUNTIF($C$15:$C$18,$B26))</f>
+        <v/>
+      </c>
+      <c r="D26" s="45" t="str">
+        <f aca="false">IF($B26="","",COUNTIF($D$15:$D$18,$B26))</f>
+        <v/>
+      </c>
+      <c r="E26" s="45" t="str">
+        <f aca="false">IF($B26="","",COUNTIF($E$15:$E$18,$B26))</f>
+        <v/>
+      </c>
+      <c r="F26" s="45" t="str">
+        <f aca="false">IF($B26="","",COUNTIF($F$15:$F$18,$B26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="45" t="str">
+        <f aca="false">IF($B26="","",C26*10+D26*8+E26*7+F26*6)</f>
+        <v/>
+      </c>
+      <c r="H26" s="65" t="str">
+        <f aca="false">IF(OR($B26="",COUNTA($B$6:$B$11)&lt;=4),"",IF(C26&gt;=1,"◎内定",""))</f>
+        <v/>
+      </c>
+      <c r="I26" s="66" t="str">
+        <f aca="false">IF(OR($B26="",COUNTA($B$6:$B$11)&lt;=4),"",IF(RANK(J26,$J$22:$J$27,0)&lt;=4,"◎決勝進出",""))</f>
+        <v/>
+      </c>
+      <c r="J26" s="68" t="str">
+        <f aca="false">IF($B26="","",IF(H26&lt;&gt;"",100000,0)+G26*100+C26*10+D26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="9" t="str">
+        <f aca="false">IF($B$11="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="C27" s="45" t="str">
+        <f aca="false">IF($B27="","",COUNTIF($C$15:$C$18,$B27))</f>
+        <v/>
+      </c>
+      <c r="D27" s="45" t="str">
+        <f aca="false">IF($B27="","",COUNTIF($D$15:$D$18,$B27))</f>
+        <v/>
+      </c>
+      <c r="E27" s="45" t="str">
+        <f aca="false">IF($B27="","",COUNTIF($E$15:$E$18,$B27))</f>
+        <v/>
+      </c>
+      <c r="F27" s="45" t="str">
+        <f aca="false">IF($B27="","",COUNTIF($F$15:$F$18,$B27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="45" t="str">
+        <f aca="false">IF($B27="","",C27*10+D27*8+E27*7+F27*6)</f>
+        <v/>
+      </c>
+      <c r="H27" s="65" t="str">
+        <f aca="false">IF(OR($B27="",COUNTA($B$6:$B$11)&lt;=4),"",IF(C27&gt;=1,"◎内定",""))</f>
+        <v/>
+      </c>
+      <c r="I27" s="66" t="str">
+        <f aca="false">IF(OR($B27="",COUNTA($B$6:$B$11)&lt;=4),"",IF(RANK(J27,$J$22:$J$27,0)&lt;=4,"◎決勝進出",""))</f>
+        <v/>
+      </c>
+      <c r="J27" s="68" t="str">
+        <f aca="false">IF($B27="","",IF(H27&lt;&gt;"",100000,0)+G27*100+C27*10+D27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="51" t="s">
+        <v>198</v>
+      </c>
+      <c r="C29" s="51"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="51"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="69" t="s">
+        <v>199</v>
+      </c>
+      <c r="C30" s="69"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+      <c r="I30" s="69"/>
+      <c r="J30" s="69"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="B30:J30"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="①の応募一覧に入力した部門名から選んでください。" errorStyle="stop" errorTitle="入力値エラー" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C15:F18" type="list">
+      <formula1>$B$6:$B$11</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -16225,7 +18141,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="23" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -16234,203 +18150,203 @@
       <c r="F1" s="23"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="56" t="s">
-        <v>185</v>
+      <c r="B3" s="70" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7"/>
       <c r="B4" s="8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="E4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="57" t="s">
-        <v>188</v>
+      <c r="B5" s="71" t="s">
+        <v>204</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="57" t="s">
-        <v>191</v>
+      <c r="B6" s="71" t="s">
+        <v>207</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="57" t="s">
-        <v>194</v>
+      <c r="B7" s="71" t="s">
+        <v>210</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="57" t="s">
-        <v>197</v>
+      <c r="B8" s="71" t="s">
+        <v>213</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="56" t="s">
-        <v>200</v>
+      <c r="B10" s="70" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7"/>
       <c r="B11" s="7" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="9" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="E12" s="58" t="s">
-        <v>208</v>
+        <v>223</v>
+      </c>
+      <c r="E12" s="72" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="9" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="E13" s="58" t="s">
-        <v>212</v>
+        <v>227</v>
+      </c>
+      <c r="E13" s="72" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="9" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="E14" s="58" t="s">
-        <v>216</v>
+        <v>231</v>
+      </c>
+      <c r="E14" s="72" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="9" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="E15" s="58" t="s">
-        <v>220</v>
+        <v>235</v>
+      </c>
+      <c r="E15" s="72" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="51" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="C16" s="51"/>
       <c r="D16" s="51"/>
       <c r="E16" s="51"/>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="56" t="s">
-        <v>222</v>
+      <c r="B19" s="70" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="53" t="s">
-        <v>223</v>
-      </c>
-      <c r="C20" s="59" t="s">
-        <v>224</v>
-      </c>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
+        <v>239</v>
+      </c>
+      <c r="C20" s="73" t="s">
+        <v>240</v>
+      </c>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="53" t="s">
-        <v>225</v>
-      </c>
-      <c r="C21" s="59" t="s">
-        <v>226</v>
-      </c>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
+        <v>241</v>
+      </c>
+      <c r="C21" s="73" t="s">
+        <v>242</v>
+      </c>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="53" t="s">
-        <v>227</v>
-      </c>
-      <c r="C22" s="59" t="s">
-        <v>228</v>
-      </c>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
+        <v>243</v>
+      </c>
+      <c r="C22" s="73" t="s">
+        <v>244</v>
+      </c>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="53" t="s">
-        <v>229</v>
-      </c>
-      <c r="C23" s="59" t="s">
-        <v>230</v>
-      </c>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
+        <v>245</v>
+      </c>
+      <c r="C23" s="74" t="s">
+        <v>246</v>
+      </c>
+      <c r="D23" s="74"/>
+      <c r="E23" s="74"/>
     </row>
     <row r="25" customFormat="false" ht="25.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="60" t="s">
-        <v>231</v>
-      </c>
-      <c r="C25" s="60"/>
-      <c r="D25" s="60"/>
-      <c r="E25" s="60"/>
+      <c r="B25" s="75" t="s">
+        <v>247</v>
+      </c>
+      <c r="C25" s="75"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -16452,7 +18368,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -16467,1292 +18383,1292 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="61" t="s">
-        <v>233</v>
+      <c r="B3" s="60" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="62" t="s">
-        <v>234</v>
+      <c r="B4" s="76" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="62"/>
+      <c r="B5" s="76"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="62" t="s">
-        <v>235</v>
+      <c r="B6" s="76" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="62" t="s">
-        <v>236</v>
+      <c r="B7" s="76" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="62"/>
+      <c r="B8" s="76"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="63" t="s">
-        <v>237</v>
+      <c r="B9" s="77" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="62" t="s">
-        <v>238</v>
+      <c r="B10" s="76" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="63" t="s">
-        <v>237</v>
+      <c r="B11" s="77" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="63" t="s">
-        <v>239</v>
+      <c r="B12" s="77" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="63" t="s">
-        <v>240</v>
+      <c r="B13" s="77" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="63" t="s">
-        <v>241</v>
+      <c r="B14" s="77" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="63" t="s">
-        <v>242</v>
+      <c r="B15" s="77" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="63" t="s">
-        <v>243</v>
+      <c r="B16" s="77" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="63" t="s">
-        <v>244</v>
+      <c r="B17" s="77" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="62"/>
+      <c r="B18" s="76"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="63" t="s">
-        <v>237</v>
+      <c r="B19" s="77" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="62" t="s">
-        <v>245</v>
+      <c r="B20" s="76" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="63" t="s">
-        <v>237</v>
+      <c r="B21" s="77" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="62"/>
+      <c r="B22" s="76"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="63" t="s">
-        <v>246</v>
+      <c r="B23" s="77" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="62" t="s">
-        <v>247</v>
+      <c r="B24" s="76" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="62" t="s">
-        <v>248</v>
+      <c r="B25" s="76" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="63" t="s">
-        <v>246</v>
+      <c r="B26" s="77" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="62" t="s">
-        <v>249</v>
+      <c r="B27" s="76" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="62"/>
+      <c r="B28" s="76"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="62" t="s">
-        <v>250</v>
+      <c r="B29" s="76" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="62" t="s">
-        <v>251</v>
+      <c r="B30" s="76" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="62" t="s">
-        <v>252</v>
+      <c r="B31" s="76" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="62" t="s">
+      <c r="B32" s="76" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="76" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="76"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="76" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="76" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="76" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="76" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="76" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="76" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="76" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="76"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="77" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="76" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="76" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="77" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="76" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="76"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="76" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="76" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="76" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="76" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="76" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="76"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="76" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="76" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="76" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="76" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="76"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="77" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="76" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="76" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="77" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="76" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="76"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="76" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="76" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="76" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="76" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="76" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="76"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="76" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="76" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="76" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="76" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="76" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="76"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="77" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="76" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="76" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="77" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="76" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="76"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="76" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="76" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="76" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="76" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B88" s="76" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="76"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B90" s="76" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B91" s="76" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B92" s="76" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B93" s="76" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B94" s="76"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B95" s="77" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B96" s="76" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B97" s="76" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B98" s="77" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B99" s="76" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B100" s="76"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B101" s="76" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B102" s="76" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B103" s="76" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B104" s="76" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B105" s="76" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B106" s="76"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B107" s="76" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="76" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="76" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="76" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B111" s="76"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B112" s="77" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B113" s="76" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B114" s="76" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B115" s="77" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B116" s="76" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B117" s="76"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B118" s="76" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B119" s="76" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B120" s="76" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B121" s="76" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B122" s="76" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B123" s="76"/>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B124" s="76" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B125" s="76" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B126" s="76" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B127" s="76" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B128" s="76" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B129" s="76" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B130" s="76" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B131" s="76"/>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B132" s="77" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="62" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="62"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="62" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="62" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="62" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="62" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="62" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="62" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="62" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="62"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="63" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="62" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="62" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="63" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="62" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="62"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="62" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="62" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="62" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="62" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="62" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="62"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="62" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="62" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="62" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="62" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="62"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="63" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="62" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="62" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="63" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="62" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="62"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="62" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="62" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="62" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="62" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="62" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="62"/>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="62" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="62" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="62" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="62" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="62" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="62"/>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="63" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="62" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="62" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="63" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="62" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="62"/>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="62" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="62" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="62" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="62" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B88" s="62" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="62"/>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="62" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="62" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="62" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="62" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="62"/>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B95" s="63" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B96" s="62" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B97" s="62" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B98" s="63" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="62" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B100" s="62"/>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B101" s="62" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B102" s="62" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B103" s="62" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B104" s="62" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B105" s="62" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B106" s="62"/>
-    </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B107" s="62" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B108" s="62" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B109" s="62" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="62" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="62"/>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B112" s="63" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B113" s="62" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B114" s="62" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B115" s="63" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B116" s="62" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B117" s="62"/>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B118" s="62" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B119" s="62" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B120" s="62" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B121" s="62" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="62" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B123" s="62"/>
-    </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B124" s="62" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B125" s="62" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B126" s="62" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B127" s="62" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B128" s="62" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B129" s="62" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B130" s="62" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B131" s="62"/>
-    </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B132" s="63" t="s">
-        <v>237</v>
-      </c>
-    </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B133" s="62" t="s">
-        <v>321</v>
+      <c r="B133" s="76" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B134" s="63" t="s">
-        <v>237</v>
+      <c r="B134" s="77" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B135" s="62"/>
+      <c r="B135" s="76"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B136" s="63" t="s">
-        <v>322</v>
+      <c r="B136" s="77" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B137" s="62" t="s">
-        <v>323</v>
+      <c r="B137" s="76" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B138" s="62" t="s">
-        <v>324</v>
+      <c r="B138" s="76" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B139" s="62" t="s">
-        <v>325</v>
+      <c r="B139" s="76" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B140" s="62"/>
+      <c r="B140" s="76"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B141" s="63" t="s">
-        <v>326</v>
+      <c r="B141" s="77" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B142" s="62" t="s">
-        <v>327</v>
+      <c r="B142" s="76" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B143" s="62" t="s">
-        <v>328</v>
+      <c r="B143" s="76" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B144" s="62" t="s">
-        <v>329</v>
+      <c r="B144" s="76" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B145" s="62"/>
+      <c r="B145" s="76"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B146" s="63" t="s">
-        <v>330</v>
+      <c r="B146" s="77" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B147" s="62" t="s">
-        <v>331</v>
+      <c r="B147" s="76" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B148" s="62" t="s">
-        <v>332</v>
+      <c r="B148" s="76" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B149" s="62" t="s">
-        <v>333</v>
+      <c r="B149" s="76" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B150" s="62"/>
+      <c r="B150" s="76"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B151" s="63" t="s">
-        <v>334</v>
+      <c r="B151" s="77" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B152" s="62" t="s">
-        <v>335</v>
+      <c r="B152" s="76" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B153" s="62" t="s">
-        <v>336</v>
+      <c r="B153" s="76" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B154" s="62" t="s">
-        <v>337</v>
+      <c r="B154" s="76" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B155" s="62"/>
+      <c r="B155" s="76"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B156" s="63" t="s">
-        <v>237</v>
+      <c r="B156" s="77" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B157" s="62" t="s">
-        <v>338</v>
+      <c r="B157" s="76" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B158" s="63" t="s">
-        <v>237</v>
+      <c r="B158" s="77" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B159" s="63" t="s">
-        <v>339</v>
+      <c r="B159" s="77" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B160" s="63" t="s">
-        <v>340</v>
+      <c r="B160" s="77" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B161" s="63" t="s">
-        <v>341</v>
+      <c r="B161" s="77" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B162" s="63" t="s">
-        <v>342</v>
+      <c r="B162" s="77" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B163" s="62"/>
-    </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B164" s="62" t="s">
-        <v>343</v>
+      <c r="B163" s="76"/>
+    </row>
+    <row r="164" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B164" s="76" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B165" s="62"/>
+      <c r="B165" s="76"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B166" s="63" t="s">
-        <v>237</v>
+      <c r="B166" s="77" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B167" s="62" t="s">
-        <v>344</v>
+      <c r="B167" s="76" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B168" s="63" t="s">
-        <v>237</v>
+      <c r="B168" s="77" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B169" s="63" t="s">
-        <v>345</v>
+      <c r="B169" s="77" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B170" s="63" t="s">
-        <v>346</v>
+      <c r="B170" s="77" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B171" s="63" t="s">
-        <v>347</v>
+      <c r="B171" s="77" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B172" s="63" t="s">
-        <v>348</v>
+      <c r="B172" s="77" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B173" s="63" t="s">
-        <v>349</v>
+      <c r="B173" s="77" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B174" s="63" t="s">
-        <v>350</v>
+      <c r="B174" s="77" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B175" s="63" t="s">
-        <v>351</v>
+      <c r="B175" s="77" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B176" s="63" t="s">
-        <v>352</v>
+      <c r="B176" s="77" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B177" s="63" t="s">
-        <v>353</v>
+      <c r="B177" s="77" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B178" s="63" t="s">
-        <v>354</v>
+      <c r="B178" s="77" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B179" s="63" t="s">
-        <v>355</v>
+      <c r="B179" s="77" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B180" s="63" t="s">
-        <v>356</v>
+      <c r="B180" s="77" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B181" s="63" t="s">
-        <v>357</v>
+      <c r="B181" s="77" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B182" s="63" t="s">
-        <v>349</v>
+      <c r="B182" s="77" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B183" s="63" t="s">
-        <v>358</v>
+      <c r="B183" s="77" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B184" s="63" t="s">
-        <v>359</v>
+      <c r="B184" s="77" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B185" s="63" t="s">
-        <v>352</v>
+      <c r="B185" s="77" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B186" s="63" t="s">
-        <v>353</v>
+      <c r="B186" s="77" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B187" s="63" t="s">
-        <v>354</v>
+      <c r="B187" s="77" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B188" s="63" t="s">
-        <v>355</v>
+      <c r="B188" s="77" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B189" s="63" t="s">
-        <v>356</v>
+      <c r="B189" s="77" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B190" s="63" t="s">
-        <v>357</v>
+      <c r="B190" s="77" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B191" s="63" t="s">
-        <v>349</v>
+      <c r="B191" s="77" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B192" s="63" t="s">
-        <v>360</v>
+      <c r="B192" s="77" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B193" s="63" t="s">
-        <v>361</v>
+      <c r="B193" s="77" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B194" s="63" t="s">
-        <v>352</v>
+      <c r="B194" s="77" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B195" s="63" t="s">
-        <v>362</v>
+      <c r="B195" s="77" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B196" s="63" t="s">
-        <v>354</v>
+      <c r="B196" s="77" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B197" s="63" t="s">
-        <v>355</v>
+      <c r="B197" s="77" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B198" s="63" t="s">
-        <v>356</v>
+      <c r="B198" s="77" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B199" s="63" t="s">
-        <v>357</v>
+      <c r="B199" s="77" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B200" s="63" t="s">
-        <v>349</v>
+      <c r="B200" s="77" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B201" s="63" t="s">
-        <v>363</v>
+      <c r="B201" s="77" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B202" s="63" t="s">
-        <v>364</v>
+      <c r="B202" s="77" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B203" s="63" t="s">
-        <v>352</v>
+      <c r="B203" s="77" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B204" s="63" t="s">
-        <v>362</v>
+      <c r="B204" s="77" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B205" s="63" t="s">
-        <v>354</v>
+      <c r="B205" s="77" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B206" s="63" t="s">
-        <v>355</v>
+      <c r="B206" s="77" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B207" s="63" t="s">
-        <v>356</v>
+      <c r="B207" s="77" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B208" s="63" t="s">
-        <v>357</v>
+      <c r="B208" s="77" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B209" s="63" t="s">
-        <v>349</v>
+      <c r="B209" s="77" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B210" s="63" t="s">
+      <c r="B210" s="77" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B211" s="77" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B212" s="77" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B213" s="77" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B214" s="77" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B215" s="77" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B216" s="77" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B217" s="77" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B218" s="77" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B211" s="63" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B212" s="63" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B213" s="63" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B214" s="63" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B215" s="63" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B216" s="63" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B217" s="63" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B218" s="63" t="s">
-        <v>349</v>
-      </c>
-    </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B219" s="63" t="s">
-        <v>367</v>
+      <c r="B219" s="77" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B220" s="63" t="s">
+      <c r="B220" s="77" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B221" s="77" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B221" s="63" t="s">
-        <v>352</v>
-      </c>
-    </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B222" s="63" t="s">
-        <v>369</v>
+      <c r="B222" s="77" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B223" s="63" t="s">
-        <v>354</v>
+      <c r="B223" s="77" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B224" s="63" t="s">
-        <v>355</v>
+      <c r="B224" s="77" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B225" s="63" t="s">
-        <v>356</v>
+      <c r="B225" s="77" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B226" s="63" t="s">
-        <v>370</v>
+      <c r="B226" s="77" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B227" s="63" t="s">
-        <v>371</v>
+      <c r="B227" s="77" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B228" s="63" t="s">
-        <v>372</v>
+      <c r="B228" s="77" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B229" s="63" t="s">
-        <v>349</v>
+      <c r="B229" s="77" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B230" s="63" t="s">
+      <c r="B230" s="77" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B231" s="77" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B232" s="77" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B233" s="77" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B231" s="63" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B232" s="63" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B233" s="63" t="s">
-        <v>357</v>
-      </c>
-    </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B234" s="63" t="s">
-        <v>349</v>
+      <c r="B234" s="77" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B235" s="63" t="s">
-        <v>376</v>
+      <c r="B235" s="77" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B236" s="63" t="s">
-        <v>374</v>
+      <c r="B236" s="77" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B237" s="63" t="s">
-        <v>375</v>
+      <c r="B237" s="77" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B238" s="63" t="s">
-        <v>357</v>
+      <c r="B238" s="77" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B239" s="63" t="s">
-        <v>349</v>
+      <c r="B239" s="77" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B240" s="63" t="s">
-        <v>377</v>
+      <c r="B240" s="77" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B241" s="63" t="s">
-        <v>374</v>
+      <c r="B241" s="77" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B242" s="63" t="s">
-        <v>375</v>
+      <c r="B242" s="77" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B243" s="63" t="s">
-        <v>357</v>
+      <c r="B243" s="77" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B244" s="63" t="s">
-        <v>349</v>
+      <c r="B244" s="77" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B245" s="63" t="s">
-        <v>378</v>
+      <c r="B245" s="77" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B246" s="63" t="s">
-        <v>374</v>
+      <c r="B246" s="77" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B247" s="63" t="s">
-        <v>375</v>
+      <c r="B247" s="77" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B248" s="63" t="s">
-        <v>370</v>
+      <c r="B248" s="77" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B249" s="63" t="s">
-        <v>371</v>
+      <c r="B249" s="77" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B250" s="63" t="s">
-        <v>379</v>
+      <c r="B250" s="77" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B251" s="63" t="s">
-        <v>380</v>
+      <c r="B251" s="77" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B252" s="63" t="s">
-        <v>381</v>
+      <c r="B252" s="77" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B253" s="63" t="s">
-        <v>382</v>
+      <c r="B253" s="77" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B254" s="63" t="s">
-        <v>383</v>
+      <c r="B254" s="77" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B255" s="63" t="s">
-        <v>384</v>
+      <c r="B255" s="77" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B256" s="63" t="s">
-        <v>385</v>
+      <c r="B256" s="77" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B257" s="63" t="s">
-        <v>386</v>
+      <c r="B257" s="77" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B258" s="63" t="s">
-        <v>387</v>
+      <c r="B258" s="77" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B259" s="62"/>
+      <c r="B259" s="76"/>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B260" s="63" t="s">
-        <v>237</v>
+      <c r="B260" s="77" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B261" s="62" t="s">
-        <v>388</v>
+      <c r="B261" s="76" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B262" s="63" t="s">
-        <v>237</v>
+      <c r="B262" s="77" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B263" s="62" t="s">
-        <v>389</v>
+      <c r="B263" s="76" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B264" s="62" t="s">
-        <v>390</v>
+      <c r="B264" s="76" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B265" s="62" t="s">
-        <v>391</v>
+      <c r="B265" s="76" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B266" s="62" t="s">
-        <v>392</v>
+      <c r="B266" s="76" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B267" s="62" t="s">
-        <v>393</v>
+      <c r="B267" s="76" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B268" s="62"/>
+      <c r="B268" s="76"/>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B269" s="63" t="s">
-        <v>237</v>
+      <c r="B269" s="77" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B270" s="62" t="s">
-        <v>394</v>
+      <c r="B270" s="76" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B271" s="63" t="s">
-        <v>237</v>
+      <c r="B271" s="77" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -17769,7 +19685,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -17786,7 +19702,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="23" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -17796,7 +19712,7 @@
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -17806,22 +19722,22 @@
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17829,19 +19745,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="E4" s="64" t="s">
-        <v>401</v>
-      </c>
-      <c r="F4" s="65" t="s">
-        <v>402</v>
+        <v>416</v>
+      </c>
+      <c r="E4" s="78" t="s">
+        <v>417</v>
+      </c>
+      <c r="F4" s="79" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17849,19 +19765,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="E5" s="64" t="s">
-        <v>404</v>
-      </c>
-      <c r="F5" s="65" t="s">
-        <v>405</v>
+        <v>419</v>
+      </c>
+      <c r="E5" s="78" t="s">
+        <v>420</v>
+      </c>
+      <c r="F5" s="79" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17869,19 +19785,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="E6" s="64" t="s">
-        <v>407</v>
-      </c>
-      <c r="F6" s="65" t="s">
-        <v>408</v>
+        <v>422</v>
+      </c>
+      <c r="E6" s="78" t="s">
+        <v>423</v>
+      </c>
+      <c r="F6" s="79" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17889,19 +19805,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="E7" s="66" t="s">
-        <v>409</v>
-      </c>
-      <c r="F7" s="67" t="s">
-        <v>410</v>
+        <v>422</v>
+      </c>
+      <c r="E7" s="80" t="s">
+        <v>425</v>
+      </c>
+      <c r="F7" s="81" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17909,19 +19825,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="E8" s="66" t="s">
-        <v>412</v>
-      </c>
-      <c r="F8" s="65" t="s">
-        <v>413</v>
+        <v>427</v>
+      </c>
+      <c r="E8" s="80" t="s">
+        <v>428</v>
+      </c>
+      <c r="F8" s="79" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17929,19 +19845,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="E9" s="66" t="s">
-        <v>414</v>
-      </c>
-      <c r="F9" s="65" t="s">
-        <v>415</v>
+        <v>419</v>
+      </c>
+      <c r="E9" s="80" t="s">
+        <v>430</v>
+      </c>
+      <c r="F9" s="79" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17949,19 +19865,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="E10" s="64" t="s">
-        <v>416</v>
-      </c>
-      <c r="F10" s="67" t="s">
-        <v>417</v>
+        <v>427</v>
+      </c>
+      <c r="E10" s="78" t="s">
+        <v>432</v>
+      </c>
+      <c r="F10" s="81" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17969,19 +19885,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="E11" s="64" t="s">
-        <v>419</v>
-      </c>
-      <c r="F11" s="65" t="s">
-        <v>420</v>
+        <v>434</v>
+      </c>
+      <c r="E11" s="78" t="s">
+        <v>435</v>
+      </c>
+      <c r="F11" s="79" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17989,19 +19905,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="E12" s="64" t="s">
-        <v>422</v>
-      </c>
-      <c r="F12" s="65" t="s">
-        <v>423</v>
+        <v>437</v>
+      </c>
+      <c r="E12" s="78" t="s">
+        <v>438</v>
+      </c>
+      <c r="F12" s="79" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18009,19 +19925,19 @@
         <v>10</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="E13" s="66" t="s">
-        <v>425</v>
-      </c>
-      <c r="F13" s="65" t="s">
-        <v>426</v>
+        <v>440</v>
+      </c>
+      <c r="E13" s="80" t="s">
+        <v>441</v>
+      </c>
+      <c r="F13" s="79" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18029,19 +19945,19 @@
         <v>11</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="E14" s="66" t="s">
-        <v>428</v>
-      </c>
-      <c r="F14" s="67" t="s">
-        <v>429</v>
+        <v>443</v>
+      </c>
+      <c r="E14" s="80" t="s">
+        <v>444</v>
+      </c>
+      <c r="F14" s="81" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18049,19 +19965,19 @@
         <v>12</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="E15" s="66" t="s">
-        <v>430</v>
-      </c>
-      <c r="F15" s="65" t="s">
-        <v>431</v>
+        <v>416</v>
+      </c>
+      <c r="E15" s="80" t="s">
+        <v>446</v>
+      </c>
+      <c r="F15" s="79" t="s">
+        <v>447</v>
       </c>
     </row>
   </sheetData>
